--- a/output/yearly_population_iteration_70_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_70_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7284</v>
+        <v>4962</v>
       </c>
       <c r="C2" t="n">
-        <v>10229</v>
+        <v>6661</v>
       </c>
       <c r="D2" t="n">
-        <v>29124</v>
+        <v>27925</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4144</v>
+        <v>2886</v>
       </c>
       <c r="C3" t="n">
-        <v>4145</v>
+        <v>4378</v>
       </c>
       <c r="D3" t="n">
-        <v>15679</v>
+        <v>15765</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2909</v>
+        <v>2236</v>
       </c>
       <c r="C4" t="n">
-        <v>4861</v>
+        <v>6231</v>
       </c>
       <c r="D4" t="n">
-        <v>6879</v>
+        <v>6578</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2000</v>
+        <v>1520</v>
       </c>
       <c r="C5" t="n">
-        <v>3871</v>
+        <v>5074</v>
       </c>
       <c r="D5" t="n">
-        <v>2538</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1212</v>
+        <v>888</v>
       </c>
       <c r="C6" t="n">
-        <v>2613</v>
+        <v>2821</v>
       </c>
       <c r="D6" t="n">
-        <v>1098</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>570</v>
+        <v>414</v>
       </c>
       <c r="C7" t="n">
-        <v>1795</v>
+        <v>1843</v>
       </c>
       <c r="D7" t="n">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>212</v>
+        <v>160</v>
       </c>
       <c r="C8" t="n">
-        <v>965</v>
+        <v>993</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
         <v>160</v>
@@ -951,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9390</v>
+        <v>5252</v>
       </c>
       <c r="C2" t="n">
-        <v>8993</v>
+        <v>18461</v>
       </c>
       <c r="D2" t="n">
-        <v>37426</v>
+        <v>30234</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4495</v>
+        <v>3093</v>
       </c>
       <c r="C3" t="n">
-        <v>6081</v>
+        <v>4765</v>
       </c>
       <c r="D3" t="n">
-        <v>16453</v>
+        <v>16359</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2969</v>
+        <v>2175</v>
       </c>
       <c r="C4" t="n">
-        <v>4369</v>
+        <v>5152</v>
       </c>
       <c r="D4" t="n">
-        <v>8106</v>
+        <v>7877</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2118</v>
+        <v>1618</v>
       </c>
       <c r="C5" t="n">
-        <v>4256</v>
+        <v>5512</v>
       </c>
       <c r="D5" t="n">
-        <v>3103</v>
+        <v>2975</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1415</v>
+        <v>1056</v>
       </c>
       <c r="C6" t="n">
-        <v>3129</v>
+        <v>3782</v>
       </c>
       <c r="D6" t="n">
-        <v>1304</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>762</v>
+        <v>556</v>
       </c>
       <c r="C7" t="n">
-        <v>2163</v>
+        <v>2283</v>
       </c>
       <c r="D7" t="n">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>316</v>
+        <v>233</v>
       </c>
       <c r="C8" t="n">
-        <v>1313</v>
+        <v>1349</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>647</v>
+        <v>667</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1220,7 +1220,7 @@
         <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1262,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10041</v>
+        <v>6548</v>
       </c>
       <c r="C2" t="n">
-        <v>7669</v>
+        <v>18241</v>
       </c>
       <c r="D2" t="n">
-        <v>32565</v>
+        <v>27068</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5228</v>
+        <v>3230</v>
       </c>
       <c r="C3" t="n">
-        <v>6461</v>
+        <v>9309</v>
       </c>
       <c r="D3" t="n">
-        <v>18216</v>
+        <v>16977</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3048</v>
+        <v>2168</v>
       </c>
       <c r="C4" t="n">
-        <v>5034</v>
+        <v>4828</v>
       </c>
       <c r="D4" t="n">
-        <v>8983</v>
+        <v>8783</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2188</v>
+        <v>1657</v>
       </c>
       <c r="C5" t="n">
-        <v>4174</v>
+        <v>5192</v>
       </c>
       <c r="D5" t="n">
-        <v>3699</v>
+        <v>3561</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1567</v>
+        <v>1167</v>
       </c>
       <c r="C6" t="n">
-        <v>3566</v>
+        <v>4462</v>
       </c>
       <c r="D6" t="n">
-        <v>1545</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>916</v>
+        <v>675</v>
       </c>
       <c r="C7" t="n">
-        <v>2529</v>
+        <v>2862</v>
       </c>
       <c r="D7" t="n">
-        <v>767</v>
+        <v>762</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>430</v>
+        <v>315</v>
       </c>
       <c r="C8" t="n">
-        <v>1632</v>
+        <v>1701</v>
       </c>
       <c r="D8" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="C9" t="n">
-        <v>901</v>
+        <v>927</v>
       </c>
       <c r="D9" t="n">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C10" t="n">
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
         <v>167</v>
@@ -1573,7 +1573,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>103</v>
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9157</v>
+        <v>5960</v>
       </c>
       <c r="C2" t="n">
-        <v>5214</v>
+        <v>12403</v>
       </c>
       <c r="D2" t="n">
-        <v>26751</v>
+        <v>22469</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5937</v>
+        <v>3883</v>
       </c>
       <c r="C3" t="n">
-        <v>9152</v>
+        <v>13118</v>
       </c>
       <c r="D3" t="n">
-        <v>19547</v>
+        <v>18181</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2021</v>
+        <v>1531</v>
       </c>
       <c r="C4" t="n">
-        <v>6809</v>
+        <v>7626</v>
       </c>
       <c r="D4" t="n">
-        <v>8420</v>
+        <v>8194</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1447</v>
+        <v>1078</v>
       </c>
       <c r="C5" t="n">
-        <v>3494</v>
+        <v>4372</v>
       </c>
       <c r="D5" t="n">
-        <v>2508</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>846</v>
+        <v>623</v>
       </c>
       <c r="C6" t="n">
-        <v>2478</v>
+        <v>2804</v>
       </c>
       <c r="D6" t="n">
-        <v>751</v>
+        <v>746</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>397</v>
+        <v>291</v>
       </c>
       <c r="C7" t="n">
-        <v>1599</v>
+        <v>1666</v>
       </c>
       <c r="D7" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
-        <v>882</v>
+        <v>908</v>
       </c>
       <c r="D8" t="n">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
         <v>163</v>
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
         <v>77</v>
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5632</v>
+        <v>3561</v>
       </c>
       <c r="C2" t="n">
-        <v>2535</v>
+        <v>5534</v>
       </c>
       <c r="D2" t="n">
-        <v>18882</v>
+        <v>15526</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6268</v>
+        <v>4090</v>
       </c>
       <c r="C3" t="n">
-        <v>6737</v>
+        <v>11608</v>
       </c>
       <c r="D3" t="n">
-        <v>19400</v>
+        <v>17891</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3011</v>
+        <v>2103</v>
       </c>
       <c r="C4" t="n">
-        <v>7943</v>
+        <v>10290</v>
       </c>
       <c r="D4" t="n">
-        <v>10034</v>
+        <v>9461</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1593</v>
+        <v>1192</v>
       </c>
       <c r="C5" t="n">
-        <v>4957</v>
+        <v>5760</v>
       </c>
       <c r="D5" t="n">
-        <v>3217</v>
+        <v>3122</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>995</v>
+        <v>737</v>
       </c>
       <c r="C6" t="n">
-        <v>2956</v>
+        <v>3516</v>
       </c>
       <c r="D6" t="n">
-        <v>932</v>
+        <v>920</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>374</v>
+        <v>273</v>
       </c>
       <c r="C7" t="n">
-        <v>1980</v>
+        <v>2097</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>1133</v>
+        <v>1174</v>
       </c>
       <c r="D8" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D10" t="n">
         <v>211</v>
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
         <v>167</v>
@@ -2167,7 +2167,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
         <v>97</v>
@@ -2195,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5828</v>
+        <v>3217</v>
       </c>
       <c r="C2" t="n">
-        <v>3335</v>
+        <v>9356</v>
       </c>
       <c r="D2" t="n">
-        <v>25209</v>
+        <v>19940</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5034</v>
+        <v>3252</v>
       </c>
       <c r="C3" t="n">
-        <v>4223</v>
+        <v>7718</v>
       </c>
       <c r="D3" t="n">
-        <v>18176</v>
+        <v>16367</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3807</v>
+        <v>2539</v>
       </c>
       <c r="C4" t="n">
-        <v>7187</v>
+        <v>10820</v>
       </c>
       <c r="D4" t="n">
-        <v>11257</v>
+        <v>10549</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1942</v>
+        <v>1396</v>
       </c>
       <c r="C5" t="n">
-        <v>6258</v>
+        <v>7727</v>
       </c>
       <c r="D5" t="n">
-        <v>4166</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1145</v>
+        <v>848</v>
       </c>
       <c r="C6" t="n">
-        <v>3858</v>
+        <v>4473</v>
       </c>
       <c r="D6" t="n">
-        <v>1248</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>548</v>
+        <v>399</v>
       </c>
       <c r="C7" t="n">
-        <v>2419</v>
+        <v>2728</v>
       </c>
       <c r="D7" t="n">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>187</v>
+        <v>140</v>
       </c>
       <c r="C8" t="n">
-        <v>1483</v>
+        <v>1555</v>
       </c>
       <c r="D8" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>715</v>
+        <v>741</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
         <v>170</v>
@@ -2478,7 +2478,7 @@
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
         <v>63</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3465</v>
+        <v>1926</v>
       </c>
       <c r="C2" t="n">
-        <v>1583</v>
+        <v>4473</v>
       </c>
       <c r="D2" t="n">
-        <v>17610</v>
+        <v>13926</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5040</v>
+        <v>3131</v>
       </c>
       <c r="C3" t="n">
-        <v>3796</v>
+        <v>8032</v>
       </c>
       <c r="D3" t="n">
-        <v>18500</v>
+        <v>16371</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4202</v>
+        <v>2794</v>
       </c>
       <c r="C4" t="n">
-        <v>6760</v>
+        <v>10650</v>
       </c>
       <c r="D4" t="n">
-        <v>12092</v>
+        <v>11275</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2027</v>
+        <v>1465</v>
       </c>
       <c r="C5" t="n">
-        <v>7354</v>
+        <v>9491</v>
       </c>
       <c r="D5" t="n">
-        <v>4418</v>
+        <v>4237</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>971</v>
+        <v>705</v>
       </c>
       <c r="C6" t="n">
-        <v>4710</v>
+        <v>5373</v>
       </c>
       <c r="D6" t="n">
-        <v>1227</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="7">
@@ -2716,10 +2716,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="C7" t="n">
-        <v>2614</v>
+        <v>2857</v>
       </c>
       <c r="D7" t="n">
         <v>570</v>
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>1151</v>
+        <v>1183</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
         <v>166</v>
@@ -2775,7 +2775,7 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3753</v>
+        <v>2729</v>
       </c>
       <c r="C2" t="n">
-        <v>8827</v>
+        <v>4948</v>
       </c>
       <c r="D2" t="n">
-        <v>19223</v>
+        <v>11765</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3712</v>
+        <v>2270</v>
       </c>
       <c r="C3" t="n">
-        <v>2467</v>
+        <v>5762</v>
       </c>
       <c r="D3" t="n">
-        <v>17135</v>
+        <v>15095</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4008</v>
+        <v>2561</v>
       </c>
       <c r="C4" t="n">
-        <v>5261</v>
+        <v>9324</v>
       </c>
       <c r="D4" t="n">
-        <v>12770</v>
+        <v>11714</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2562</v>
+        <v>1767</v>
       </c>
       <c r="C5" t="n">
-        <v>7003</v>
+        <v>9794</v>
       </c>
       <c r="D5" t="n">
-        <v>5504</v>
+        <v>5121</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1254</v>
+        <v>901</v>
       </c>
       <c r="C6" t="n">
-        <v>5829</v>
+        <v>7129</v>
       </c>
       <c r="D6" t="n">
-        <v>1639</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>366</v>
+        <v>263</v>
       </c>
       <c r="C7" t="n">
-        <v>3506</v>
+        <v>3845</v>
       </c>
       <c r="D7" t="n">
-        <v>653</v>
+        <v>638</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>1703</v>
+        <v>1796</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3075,7 +3075,7 @@
         <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
+        <v>136</v>
+      </c>
+      <c r="D11" t="n">
         <v>134</v>
-      </c>
-      <c r="D11" t="n">
-        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
         <v>99</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3173,7 +3173,7 @@
         <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2784</v>
+        <v>1840</v>
       </c>
       <c r="C2" t="n">
-        <v>5245</v>
+        <v>3213</v>
       </c>
       <c r="D2" t="n">
-        <v>14252</v>
+        <v>9542</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3264</v>
+        <v>2115</v>
       </c>
       <c r="C3" t="n">
-        <v>4527</v>
+        <v>4965</v>
       </c>
       <c r="D3" t="n">
-        <v>16453</v>
+        <v>13925</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3578</v>
+        <v>2284</v>
       </c>
       <c r="C4" t="n">
-        <v>4149</v>
+        <v>7996</v>
       </c>
       <c r="D4" t="n">
-        <v>13091</v>
+        <v>11892</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2844</v>
+        <v>1894</v>
       </c>
       <c r="C5" t="n">
-        <v>6490</v>
+        <v>9803</v>
       </c>
       <c r="D5" t="n">
-        <v>6279</v>
+        <v>5759</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1481</v>
+        <v>1050</v>
       </c>
       <c r="C6" t="n">
-        <v>6435</v>
+        <v>8200</v>
       </c>
       <c r="D6" t="n">
-        <v>1985</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>341</v>
+        <v>237</v>
       </c>
       <c r="C7" t="n">
-        <v>4314</v>
+        <v>4809</v>
       </c>
       <c r="D7" t="n">
-        <v>741</v>
+        <v>709</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>2158</v>
+        <v>2307</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>687</v>
+        <v>651</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3386,7 +3386,7 @@
         <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3470,7 +3470,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5502</v>
+        <v>2250</v>
       </c>
       <c r="C2" t="n">
-        <v>4488</v>
+        <v>7710</v>
       </c>
       <c r="D2" t="n">
-        <v>15241</v>
+        <v>17016</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2603</v>
+        <v>1704</v>
       </c>
       <c r="C3" t="n">
-        <v>4321</v>
+        <v>3869</v>
       </c>
       <c r="D3" t="n">
-        <v>15135</v>
+        <v>12641</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3013</v>
+        <v>1935</v>
       </c>
       <c r="C4" t="n">
-        <v>4182</v>
+        <v>6530</v>
       </c>
       <c r="D4" t="n">
-        <v>13177</v>
+        <v>11689</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2849</v>
+        <v>1847</v>
       </c>
       <c r="C5" t="n">
-        <v>5388</v>
+        <v>8887</v>
       </c>
       <c r="D5" t="n">
-        <v>7003</v>
+        <v>6408</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1786</v>
+        <v>1233</v>
       </c>
       <c r="C6" t="n">
-        <v>6464</v>
+        <v>8732</v>
       </c>
       <c r="D6" t="n">
-        <v>2476</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>633</v>
+        <v>428</v>
       </c>
       <c r="C7" t="n">
-        <v>5102</v>
+        <v>6083</v>
       </c>
       <c r="D7" t="n">
-        <v>891</v>
+        <v>840</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>2917</v>
+        <v>3139</v>
       </c>
       <c r="D8" t="n">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>1183</v>
+        <v>1176</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D12" t="n">
         <v>93</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6959</v>
+        <v>4589</v>
       </c>
       <c r="C2" t="n">
-        <v>9377</v>
+        <v>10080</v>
       </c>
       <c r="D2" t="n">
-        <v>9148</v>
+        <v>7214</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3935</v>
+        <v>1645</v>
       </c>
       <c r="C2" t="n">
-        <v>2550</v>
+        <v>4502</v>
       </c>
       <c r="D2" t="n">
-        <v>11218</v>
+        <v>12659</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3651</v>
+        <v>2256</v>
       </c>
       <c r="C3" t="n">
-        <v>4733</v>
+        <v>5108</v>
       </c>
       <c r="D3" t="n">
-        <v>16390</v>
+        <v>13985</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4170</v>
+        <v>2695</v>
       </c>
       <c r="C4" t="n">
-        <v>6126</v>
+        <v>9441</v>
       </c>
       <c r="D4" t="n">
-        <v>13377</v>
+        <v>11861</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1729</v>
+        <v>1156</v>
       </c>
       <c r="C5" t="n">
-        <v>8585</v>
+        <v>12647</v>
       </c>
       <c r="D5" t="n">
-        <v>6322</v>
+        <v>5787</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>584</v>
+        <v>395</v>
       </c>
       <c r="C6" t="n">
-        <v>6266</v>
+        <v>7501</v>
       </c>
       <c r="D6" t="n">
-        <v>1972</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="C7" t="n">
-        <v>2858</v>
+        <v>3076</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>539</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1159</v>
+        <v>1152</v>
       </c>
       <c r="D8" t="n">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>364</v>
+        <v>345</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D11" t="n">
         <v>91</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8140</v>
+        <v>5591</v>
       </c>
       <c r="C2" t="n">
-        <v>5139</v>
+        <v>4861</v>
       </c>
       <c r="D2" t="n">
-        <v>12907</v>
+        <v>15794</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2956</v>
+        <v>1951</v>
       </c>
       <c r="C3" t="n">
-        <v>4726</v>
+        <v>5080</v>
       </c>
       <c r="D3" t="n">
-        <v>2176</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5246</v>
+        <v>4669</v>
       </c>
       <c r="C2" t="n">
-        <v>4967</v>
+        <v>4174</v>
       </c>
       <c r="D2" t="n">
-        <v>19476</v>
+        <v>17288</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4555</v>
+        <v>3095</v>
       </c>
       <c r="C3" t="n">
-        <v>4277</v>
+        <v>4274</v>
       </c>
       <c r="D3" t="n">
-        <v>3818</v>
+        <v>4057</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1318</v>
+        <v>882</v>
       </c>
       <c r="C4" t="n">
-        <v>2813</v>
+        <v>3018</v>
       </c>
       <c r="D4" t="n">
-        <v>1619</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6240</v>
+        <v>4285</v>
       </c>
       <c r="C2" t="n">
-        <v>4491</v>
+        <v>5632</v>
       </c>
       <c r="D2" t="n">
-        <v>18041</v>
+        <v>18513</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4035</v>
+        <v>3175</v>
       </c>
       <c r="C3" t="n">
-        <v>4027</v>
+        <v>3652</v>
       </c>
       <c r="D3" t="n">
-        <v>6048</v>
+        <v>5881</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2496</v>
+        <v>1682</v>
       </c>
       <c r="C4" t="n">
-        <v>3583</v>
+        <v>3666</v>
       </c>
       <c r="D4" t="n">
-        <v>1991</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>590</v>
+        <v>422</v>
       </c>
       <c r="C5" t="n">
-        <v>1633</v>
+        <v>1746</v>
       </c>
       <c r="D5" t="n">
-        <v>1226</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5319,7 +5319,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6020</v>
+        <v>4735</v>
       </c>
       <c r="C2" t="n">
-        <v>5973</v>
+        <v>8061</v>
       </c>
       <c r="D2" t="n">
-        <v>29253</v>
+        <v>20483</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4168</v>
+        <v>3044</v>
       </c>
       <c r="C3" t="n">
-        <v>3712</v>
+        <v>4065</v>
       </c>
       <c r="D3" t="n">
-        <v>7445</v>
+        <v>7387</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2785</v>
+        <v>2059</v>
       </c>
       <c r="C4" t="n">
-        <v>3747</v>
+        <v>3547</v>
       </c>
       <c r="D4" t="n">
-        <v>2670</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1262</v>
+        <v>863</v>
       </c>
       <c r="C5" t="n">
-        <v>2594</v>
+        <v>2723</v>
       </c>
       <c r="D5" t="n">
-        <v>1309</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>319</v>
+        <v>250</v>
       </c>
       <c r="C6" t="n">
-        <v>976</v>
+        <v>1032</v>
       </c>
       <c r="D6" t="n">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
         <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6301</v>
+        <v>5113</v>
       </c>
       <c r="C2" t="n">
-        <v>8671</v>
+        <v>14006</v>
       </c>
       <c r="D2" t="n">
-        <v>29189</v>
+        <v>27927</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3687</v>
+        <v>2809</v>
       </c>
       <c r="C3" t="n">
-        <v>3987</v>
+        <v>5002</v>
       </c>
       <c r="D3" t="n">
-        <v>9628</v>
+        <v>8333</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2143</v>
+        <v>1573</v>
       </c>
       <c r="C4" t="n">
-        <v>3053</v>
+        <v>3112</v>
       </c>
       <c r="D4" t="n">
-        <v>3018</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1062</v>
+        <v>758</v>
       </c>
       <c r="C5" t="n">
-        <v>2311</v>
+        <v>2304</v>
       </c>
       <c r="D5" t="n">
-        <v>1208</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>370</v>
+        <v>266</v>
       </c>
       <c r="C6" t="n">
-        <v>1207</v>
+        <v>1263</v>
       </c>
       <c r="D6" t="n">
-        <v>769</v>
+        <v>766</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
         <v>194</v>
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
         <v>148</v>
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5668</v>
+        <v>4167</v>
       </c>
       <c r="C2" t="n">
-        <v>6296</v>
+        <v>5551</v>
       </c>
       <c r="D2" t="n">
-        <v>29914</v>
+        <v>34739</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4148</v>
+        <v>3292</v>
       </c>
       <c r="C3" t="n">
-        <v>5786</v>
+        <v>8899</v>
       </c>
       <c r="D3" t="n">
-        <v>12205</v>
+        <v>11154</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2559</v>
+        <v>1925</v>
       </c>
       <c r="C4" t="n">
-        <v>3554</v>
+        <v>4208</v>
       </c>
       <c r="D4" t="n">
-        <v>4229</v>
+        <v>4007</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1431</v>
+        <v>1033</v>
       </c>
       <c r="C5" t="n">
-        <v>2675</v>
+        <v>2736</v>
       </c>
       <c r="D5" t="n">
-        <v>1536</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>658</v>
+        <v>478</v>
       </c>
       <c r="C6" t="n">
-        <v>1827</v>
+        <v>1846</v>
       </c>
       <c r="D6" t="n">
-        <v>842</v>
+        <v>833</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>213</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>867</v>
+        <v>908</v>
       </c>
       <c r="D7" t="n">
-        <v>551</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D9" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6179,10 +6179,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
         <v>240</v>
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
         <v>120</v>
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>64</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6274</v>
+        <v>4032</v>
       </c>
       <c r="C2" t="n">
-        <v>4153</v>
+        <v>3806</v>
       </c>
       <c r="D2" t="n">
-        <v>31483</v>
+        <v>32273</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4024</v>
+        <v>3063</v>
       </c>
       <c r="C3" t="n">
-        <v>5249</v>
+        <v>6122</v>
       </c>
       <c r="D3" t="n">
-        <v>14159</v>
+        <v>14124</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2865</v>
+        <v>2227</v>
       </c>
       <c r="C4" t="n">
-        <v>4744</v>
+        <v>6777</v>
       </c>
       <c r="D4" t="n">
-        <v>5631</v>
+        <v>5257</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1760</v>
+        <v>1302</v>
       </c>
       <c r="C5" t="n">
-        <v>3100</v>
+        <v>3458</v>
       </c>
       <c r="D5" t="n">
-        <v>1965</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>942</v>
+        <v>681</v>
       </c>
       <c r="C6" t="n">
-        <v>2236</v>
+        <v>2303</v>
       </c>
       <c r="D6" t="n">
-        <v>956</v>
+        <v>948</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>385</v>
+        <v>283</v>
       </c>
       <c r="C7" t="n">
-        <v>1374</v>
+        <v>1404</v>
       </c>
       <c r="D7" t="n">
-        <v>591</v>
+        <v>594</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>603</v>
+        <v>630</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6493,7 +6493,7 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>241</v>
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>155</v>
@@ -6535,7 +6535,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
         <v>123</v>
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_70_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_70_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4962</v>
+        <v>4539</v>
       </c>
       <c r="C2" t="n">
-        <v>6661</v>
+        <v>7662</v>
       </c>
       <c r="D2" t="n">
-        <v>27925</v>
+        <v>21288</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2886</v>
+        <v>3087</v>
       </c>
       <c r="C3" t="n">
-        <v>4378</v>
+        <v>3711</v>
       </c>
       <c r="D3" t="n">
-        <v>15765</v>
+        <v>13808</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2236</v>
+        <v>2486</v>
       </c>
       <c r="C4" t="n">
-        <v>6231</v>
+        <v>3953</v>
       </c>
       <c r="D4" t="n">
-        <v>6578</v>
+        <v>7129</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1520</v>
+        <v>1608</v>
       </c>
       <c r="C5" t="n">
-        <v>5074</v>
+        <v>4006</v>
       </c>
       <c r="D5" t="n">
-        <v>2437</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>888</v>
+        <v>914</v>
       </c>
       <c r="C6" t="n">
-        <v>2821</v>
+        <v>3340</v>
       </c>
       <c r="D6" t="n">
-        <v>1084</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="C7" t="n">
-        <v>1843</v>
+        <v>2234</v>
       </c>
       <c r="D7" t="n">
-        <v>646</v>
+        <v>657</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C8" t="n">
-        <v>993</v>
+        <v>1096</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="D9" t="n">
         <v>310</v>
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
         <v>244</v>
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5252</v>
+        <v>5847</v>
       </c>
       <c r="C2" t="n">
-        <v>18461</v>
+        <v>16589</v>
       </c>
       <c r="D2" t="n">
-        <v>30234</v>
+        <v>18725</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3093</v>
+        <v>3050</v>
       </c>
       <c r="C3" t="n">
-        <v>4765</v>
+        <v>4846</v>
       </c>
       <c r="D3" t="n">
-        <v>16359</v>
+        <v>13897</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2175</v>
+        <v>2375</v>
       </c>
       <c r="C4" t="n">
-        <v>5152</v>
+        <v>3716</v>
       </c>
       <c r="D4" t="n">
-        <v>7877</v>
+        <v>8002</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1618</v>
+        <v>1753</v>
       </c>
       <c r="C5" t="n">
-        <v>5512</v>
+        <v>3897</v>
       </c>
       <c r="D5" t="n">
-        <v>2975</v>
+        <v>3376</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1056</v>
+        <v>1103</v>
       </c>
       <c r="C6" t="n">
-        <v>3782</v>
+        <v>3575</v>
       </c>
       <c r="D6" t="n">
-        <v>1277</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>556</v>
+        <v>571</v>
       </c>
       <c r="C7" t="n">
-        <v>2283</v>
+        <v>2731</v>
       </c>
       <c r="D7" t="n">
-        <v>697</v>
+        <v>718</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C8" t="n">
-        <v>1349</v>
+        <v>1575</v>
       </c>
       <c r="D8" t="n">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C9" t="n">
-        <v>667</v>
+        <v>714</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D10" t="n">
         <v>250</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -1265,7 +1265,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6548</v>
+        <v>6424</v>
       </c>
       <c r="C2" t="n">
-        <v>18241</v>
+        <v>20654</v>
       </c>
       <c r="D2" t="n">
-        <v>27068</v>
+        <v>21526</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3230</v>
+        <v>3388</v>
       </c>
       <c r="C3" t="n">
-        <v>9309</v>
+        <v>8616</v>
       </c>
       <c r="D3" t="n">
-        <v>16977</v>
+        <v>13603</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2168</v>
+        <v>2262</v>
       </c>
       <c r="C4" t="n">
-        <v>4828</v>
+        <v>4137</v>
       </c>
       <c r="D4" t="n">
-        <v>8783</v>
+        <v>8664</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1657</v>
+        <v>1785</v>
       </c>
       <c r="C5" t="n">
-        <v>5192</v>
+        <v>3702</v>
       </c>
       <c r="D5" t="n">
-        <v>3561</v>
+        <v>3907</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1167</v>
+        <v>1245</v>
       </c>
       <c r="C6" t="n">
-        <v>4462</v>
+        <v>3640</v>
       </c>
       <c r="D6" t="n">
-        <v>1504</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>675</v>
+        <v>710</v>
       </c>
       <c r="C7" t="n">
-        <v>2862</v>
+        <v>3077</v>
       </c>
       <c r="D7" t="n">
-        <v>762</v>
+        <v>797</v>
       </c>
     </row>
     <row r="8">
@@ -1486,10 +1486,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C8" t="n">
-        <v>1701</v>
+        <v>2012</v>
       </c>
       <c r="D8" t="n">
         <v>486</v>
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C9" t="n">
-        <v>927</v>
+        <v>1035</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>434</v>
+        <v>457</v>
       </c>
       <c r="D10" t="n">
         <v>256</v>
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
         <v>167</v>
@@ -1559,7 +1559,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>126</v>
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1632,7 +1632,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5960</v>
+        <v>5868</v>
       </c>
       <c r="C2" t="n">
-        <v>12403</v>
+        <v>14044</v>
       </c>
       <c r="D2" t="n">
-        <v>22469</v>
+        <v>17743</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3883</v>
+        <v>4092</v>
       </c>
       <c r="C3" t="n">
-        <v>13118</v>
+        <v>12417</v>
       </c>
       <c r="D3" t="n">
-        <v>18181</v>
+        <v>15114</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1531</v>
+        <v>1649</v>
       </c>
       <c r="C4" t="n">
-        <v>7626</v>
+        <v>5857</v>
       </c>
       <c r="D4" t="n">
-        <v>8194</v>
+        <v>8439</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1078</v>
+        <v>1150</v>
       </c>
       <c r="C5" t="n">
-        <v>4372</v>
+        <v>3567</v>
       </c>
       <c r="D5" t="n">
-        <v>2431</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>623</v>
+        <v>656</v>
       </c>
       <c r="C6" t="n">
-        <v>2804</v>
+        <v>3015</v>
       </c>
       <c r="D6" t="n">
-        <v>746</v>
+        <v>781</v>
       </c>
     </row>
     <row r="7">
@@ -1783,10 +1783,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C7" t="n">
-        <v>1666</v>
+        <v>1971</v>
       </c>
       <c r="D7" t="n">
         <v>476</v>
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>908</v>
+        <v>1014</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="D9" t="n">
         <v>250</v>
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
         <v>163</v>
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
         <v>123</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1929,7 +1929,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3561</v>
+        <v>3652</v>
       </c>
       <c r="C2" t="n">
-        <v>5534</v>
+        <v>5837</v>
       </c>
       <c r="D2" t="n">
-        <v>15526</v>
+        <v>13110</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4090</v>
+        <v>4178</v>
       </c>
       <c r="C3" t="n">
-        <v>11608</v>
+        <v>11928</v>
       </c>
       <c r="D3" t="n">
-        <v>17891</v>
+        <v>14600</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2103</v>
+        <v>2239</v>
       </c>
       <c r="C4" t="n">
-        <v>10290</v>
+        <v>8926</v>
       </c>
       <c r="D4" t="n">
-        <v>9461</v>
+        <v>9369</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1192</v>
+        <v>1275</v>
       </c>
       <c r="C5" t="n">
-        <v>5760</v>
+        <v>4609</v>
       </c>
       <c r="D5" t="n">
-        <v>3122</v>
+        <v>3373</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>737</v>
+        <v>774</v>
       </c>
       <c r="C6" t="n">
-        <v>3516</v>
+        <v>3360</v>
       </c>
       <c r="D6" t="n">
-        <v>920</v>
+        <v>977</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="C7" t="n">
-        <v>2097</v>
+        <v>2430</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>1174</v>
+        <v>1322</v>
       </c>
       <c r="D8" t="n">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>471</v>
+        <v>497</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>167</v>
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2184,7 +2184,7 @@
         <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2226,7 +2226,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3217</v>
+        <v>3646</v>
       </c>
       <c r="C2" t="n">
-        <v>9356</v>
+        <v>7376</v>
       </c>
       <c r="D2" t="n">
-        <v>19940</v>
+        <v>15606</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3252</v>
+        <v>3356</v>
       </c>
       <c r="C3" t="n">
-        <v>7718</v>
+        <v>8039</v>
       </c>
       <c r="D3" t="n">
-        <v>16367</v>
+        <v>13416</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2539</v>
+        <v>2623</v>
       </c>
       <c r="C4" t="n">
-        <v>10820</v>
+        <v>10210</v>
       </c>
       <c r="D4" t="n">
-        <v>10549</v>
+        <v>9937</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1396</v>
+        <v>1497</v>
       </c>
       <c r="C5" t="n">
-        <v>7727</v>
+        <v>6543</v>
       </c>
       <c r="D5" t="n">
-        <v>4000</v>
+        <v>4191</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>848</v>
+        <v>910</v>
       </c>
       <c r="C6" t="n">
-        <v>4473</v>
+        <v>3923</v>
       </c>
       <c r="D6" t="n">
-        <v>1224</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="C7" t="n">
-        <v>2728</v>
+        <v>2853</v>
       </c>
       <c r="D7" t="n">
-        <v>567</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C8" t="n">
-        <v>1555</v>
+        <v>1779</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>741</v>
+        <v>808</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
         <v>170</v>
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2579,7 +2579,7 @@
         <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1926</v>
+        <v>2152</v>
       </c>
       <c r="C2" t="n">
-        <v>4473</v>
+        <v>3482</v>
       </c>
       <c r="D2" t="n">
-        <v>13926</v>
+        <v>10884</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3131</v>
+        <v>3333</v>
       </c>
       <c r="C3" t="n">
-        <v>8032</v>
+        <v>7571</v>
       </c>
       <c r="D3" t="n">
-        <v>16371</v>
+        <v>13343</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2794</v>
+        <v>2883</v>
       </c>
       <c r="C4" t="n">
-        <v>10650</v>
+        <v>10269</v>
       </c>
       <c r="D4" t="n">
-        <v>11275</v>
+        <v>10452</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1465</v>
+        <v>1577</v>
       </c>
       <c r="C5" t="n">
-        <v>9491</v>
+        <v>8354</v>
       </c>
       <c r="D5" t="n">
-        <v>4237</v>
+        <v>4410</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>705</v>
+        <v>749</v>
       </c>
       <c r="C6" t="n">
-        <v>5373</v>
+        <v>4850</v>
       </c>
       <c r="D6" t="n">
-        <v>1206</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C7" t="n">
-        <v>2857</v>
+        <v>3076</v>
       </c>
       <c r="D7" t="n">
-        <v>570</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>1183</v>
+        <v>1332</v>
       </c>
       <c r="D8" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -2747,7 +2747,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="D9" t="n">
         <v>287</v>
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
         <v>166</v>
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2876,7 +2876,7 @@
         <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2729</v>
+        <v>2331</v>
       </c>
       <c r="C2" t="n">
-        <v>4948</v>
+        <v>5102</v>
       </c>
       <c r="D2" t="n">
-        <v>11765</v>
+        <v>14553</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2270</v>
+        <v>2438</v>
       </c>
       <c r="C3" t="n">
-        <v>5762</v>
+        <v>5099</v>
       </c>
       <c r="D3" t="n">
-        <v>15095</v>
+        <v>12240</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2561</v>
+        <v>2704</v>
       </c>
       <c r="C4" t="n">
-        <v>9324</v>
+        <v>8884</v>
       </c>
       <c r="D4" t="n">
-        <v>11714</v>
+        <v>10578</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1767</v>
+        <v>1865</v>
       </c>
       <c r="C5" t="n">
-        <v>9794</v>
+        <v>9106</v>
       </c>
       <c r="D5" t="n">
-        <v>5121</v>
+        <v>5145</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>901</v>
+        <v>956</v>
       </c>
       <c r="C6" t="n">
-        <v>7129</v>
+        <v>6300</v>
       </c>
       <c r="D6" t="n">
-        <v>1609</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="C7" t="n">
-        <v>3845</v>
+        <v>3800</v>
       </c>
       <c r="D7" t="n">
-        <v>638</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>1796</v>
+        <v>2003</v>
       </c>
       <c r="D8" t="n">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9">
@@ -3055,10 +3055,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>594</v>
+        <v>645</v>
       </c>
       <c r="D9" t="n">
         <v>294</v>
@@ -3072,7 +3072,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
         <v>175</v>
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
         <v>134</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3117,7 +3117,7 @@
         <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3145,7 +3145,7 @@
         <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1840</v>
+        <v>1636</v>
       </c>
       <c r="C2" t="n">
-        <v>3213</v>
+        <v>3015</v>
       </c>
       <c r="D2" t="n">
-        <v>9542</v>
+        <v>11514</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2115</v>
+        <v>2106</v>
       </c>
       <c r="C3" t="n">
-        <v>4965</v>
+        <v>4635</v>
       </c>
       <c r="D3" t="n">
-        <v>13925</v>
+        <v>11969</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2284</v>
+        <v>2420</v>
       </c>
       <c r="C4" t="n">
-        <v>7996</v>
+        <v>7428</v>
       </c>
       <c r="D4" t="n">
-        <v>11892</v>
+        <v>10565</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1894</v>
+        <v>2023</v>
       </c>
       <c r="C5" t="n">
-        <v>9803</v>
+        <v>9187</v>
       </c>
       <c r="D5" t="n">
-        <v>5759</v>
+        <v>5611</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1050</v>
+        <v>1111</v>
       </c>
       <c r="C6" t="n">
-        <v>8200</v>
+        <v>7402</v>
       </c>
       <c r="D6" t="n">
-        <v>1891</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="C7" t="n">
-        <v>4809</v>
+        <v>4647</v>
       </c>
       <c r="D7" t="n">
-        <v>709</v>
+        <v>740</v>
       </c>
     </row>
     <row r="8">
@@ -3355,10 +3355,10 @@
         <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>2307</v>
+        <v>2474</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>651</v>
+        <v>728</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
         <v>63</v>
@@ -3442,7 +3442,7 @@
         <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2250</v>
+        <v>2522</v>
       </c>
       <c r="C2" t="n">
-        <v>7710</v>
+        <v>9292</v>
       </c>
       <c r="D2" t="n">
-        <v>17016</v>
+        <v>14742</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1704</v>
+        <v>1637</v>
       </c>
       <c r="C3" t="n">
-        <v>3869</v>
+        <v>3597</v>
       </c>
       <c r="D3" t="n">
-        <v>12641</v>
+        <v>11148</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1935</v>
+        <v>2009</v>
       </c>
       <c r="C4" t="n">
-        <v>6530</v>
+        <v>6049</v>
       </c>
       <c r="D4" t="n">
-        <v>11689</v>
+        <v>10446</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1847</v>
+        <v>1970</v>
       </c>
       <c r="C5" t="n">
-        <v>8887</v>
+        <v>8286</v>
       </c>
       <c r="D5" t="n">
-        <v>6408</v>
+        <v>6106</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1233</v>
+        <v>1318</v>
       </c>
       <c r="C6" t="n">
-        <v>8732</v>
+        <v>8097</v>
       </c>
       <c r="D6" t="n">
-        <v>2349</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>428</v>
+        <v>464</v>
       </c>
       <c r="C7" t="n">
-        <v>6083</v>
+        <v>5644</v>
       </c>
       <c r="D7" t="n">
-        <v>840</v>
+        <v>882</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>3139</v>
+        <v>3218</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1176</v>
+        <v>1299</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>353</v>
+        <v>382</v>
       </c>
       <c r="D10" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
         <v>64</v>
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3781,7 +3781,7 @@
         <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4589</v>
+        <v>4583</v>
       </c>
       <c r="C2" t="n">
-        <v>10080</v>
+        <v>9638</v>
       </c>
       <c r="D2" t="n">
-        <v>7214</v>
+        <v>9891</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1645</v>
+        <v>1823</v>
       </c>
       <c r="C2" t="n">
-        <v>4502</v>
+        <v>5352</v>
       </c>
       <c r="D2" t="n">
-        <v>12659</v>
+        <v>10968</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2256</v>
+        <v>2246</v>
       </c>
       <c r="C3" t="n">
-        <v>5108</v>
+        <v>5189</v>
       </c>
       <c r="D3" t="n">
-        <v>13985</v>
+        <v>12229</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2695</v>
+        <v>2845</v>
       </c>
       <c r="C4" t="n">
-        <v>9441</v>
+        <v>8777</v>
       </c>
       <c r="D4" t="n">
-        <v>11861</v>
+        <v>10791</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1156</v>
+        <v>1254</v>
       </c>
       <c r="C5" t="n">
-        <v>12647</v>
+        <v>11756</v>
       </c>
       <c r="D5" t="n">
-        <v>5787</v>
+        <v>5590</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>395</v>
+        <v>428</v>
       </c>
       <c r="C6" t="n">
-        <v>7501</v>
+        <v>7038</v>
       </c>
       <c r="D6" t="n">
-        <v>1844</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>3076</v>
+        <v>3153</v>
       </c>
       <c r="D7" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1152</v>
+        <v>1273</v>
       </c>
       <c r="D8" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>345</v>
+        <v>374</v>
       </c>
       <c r="D9" t="n">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
         <v>62</v>
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4389,7 +4389,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5591</v>
+        <v>6127</v>
       </c>
       <c r="C2" t="n">
-        <v>4861</v>
+        <v>8603</v>
       </c>
       <c r="D2" t="n">
-        <v>15794</v>
+        <v>14009</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1951</v>
+        <v>1948</v>
       </c>
       <c r="C3" t="n">
-        <v>5080</v>
+        <v>4857</v>
       </c>
       <c r="D3" t="n">
-        <v>1851</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4669</v>
+        <v>4285</v>
       </c>
       <c r="C2" t="n">
-        <v>4174</v>
+        <v>5907</v>
       </c>
       <c r="D2" t="n">
-        <v>17288</v>
+        <v>22895</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3095</v>
+        <v>3313</v>
       </c>
       <c r="C3" t="n">
-        <v>4274</v>
+        <v>6016</v>
       </c>
       <c r="D3" t="n">
-        <v>4057</v>
+        <v>4098</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="C4" t="n">
-        <v>3018</v>
+        <v>2890</v>
       </c>
       <c r="D4" t="n">
-        <v>1554</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4285</v>
+        <v>5120</v>
       </c>
       <c r="C2" t="n">
-        <v>5632</v>
+        <v>7738</v>
       </c>
       <c r="D2" t="n">
-        <v>18513</v>
+        <v>31313</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3175</v>
+        <v>3119</v>
       </c>
       <c r="C3" t="n">
-        <v>3652</v>
+        <v>5156</v>
       </c>
       <c r="D3" t="n">
-        <v>5881</v>
+        <v>6810</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1682</v>
+        <v>1780</v>
       </c>
       <c r="C4" t="n">
-        <v>3666</v>
+        <v>4600</v>
       </c>
       <c r="D4" t="n">
-        <v>1987</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C5" t="n">
-        <v>1746</v>
+        <v>1676</v>
       </c>
       <c r="D5" t="n">
-        <v>1205</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5280,7 +5280,7 @@
         <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5319,7 +5319,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4735</v>
+        <v>5245</v>
       </c>
       <c r="C2" t="n">
-        <v>8061</v>
+        <v>4374</v>
       </c>
       <c r="D2" t="n">
-        <v>20483</v>
+        <v>27174</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3044</v>
+        <v>3319</v>
       </c>
       <c r="C3" t="n">
-        <v>4065</v>
+        <v>5694</v>
       </c>
       <c r="D3" t="n">
-        <v>7387</v>
+        <v>10055</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2059</v>
+        <v>2056</v>
       </c>
       <c r="C4" t="n">
-        <v>3547</v>
+        <v>4753</v>
       </c>
       <c r="D4" t="n">
-        <v>2636</v>
+        <v>2867</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>863</v>
+        <v>900</v>
       </c>
       <c r="C5" t="n">
-        <v>2723</v>
+        <v>3156</v>
       </c>
       <c r="D5" t="n">
-        <v>1291</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C6" t="n">
-        <v>1032</v>
+        <v>982</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>951</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
         <v>189</v>
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5113</v>
+        <v>5053</v>
       </c>
       <c r="C2" t="n">
-        <v>14006</v>
+        <v>6576</v>
       </c>
       <c r="D2" t="n">
-        <v>27927</v>
+        <v>21100</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2809</v>
+        <v>3091</v>
       </c>
       <c r="C3" t="n">
-        <v>5002</v>
+        <v>4126</v>
       </c>
       <c r="D3" t="n">
-        <v>8333</v>
+        <v>11242</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1573</v>
+        <v>1667</v>
       </c>
       <c r="C4" t="n">
-        <v>3112</v>
+        <v>4269</v>
       </c>
       <c r="D4" t="n">
-        <v>2963</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="C5" t="n">
-        <v>2304</v>
+        <v>2907</v>
       </c>
       <c r="D5" t="n">
-        <v>1213</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C6" t="n">
-        <v>1263</v>
+        <v>1378</v>
       </c>
       <c r="D6" t="n">
-        <v>766</v>
+        <v>772</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>441</v>
+        <v>422</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4167</v>
+        <v>5392</v>
       </c>
       <c r="C2" t="n">
-        <v>5551</v>
+        <v>4056</v>
       </c>
       <c r="D2" t="n">
-        <v>34739</v>
+        <v>23838</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3292</v>
+        <v>3366</v>
       </c>
       <c r="C3" t="n">
-        <v>8899</v>
+        <v>4779</v>
       </c>
       <c r="D3" t="n">
-        <v>11154</v>
+        <v>12070</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1925</v>
+        <v>2065</v>
       </c>
       <c r="C4" t="n">
-        <v>4208</v>
+        <v>4093</v>
       </c>
       <c r="D4" t="n">
-        <v>4007</v>
+        <v>4974</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1033</v>
+        <v>1083</v>
       </c>
       <c r="C5" t="n">
-        <v>2736</v>
+        <v>3644</v>
       </c>
       <c r="D5" t="n">
-        <v>1528</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C6" t="n">
-        <v>1846</v>
+        <v>2227</v>
       </c>
       <c r="D6" t="n">
-        <v>833</v>
+        <v>852</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
-        <v>908</v>
+        <v>955</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6213,7 +6213,7 @@
         <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -6266,7 +6266,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4032</v>
+        <v>3921</v>
       </c>
       <c r="C2" t="n">
-        <v>3806</v>
+        <v>4665</v>
       </c>
       <c r="D2" t="n">
-        <v>32273</v>
+        <v>24369</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3063</v>
+        <v>3576</v>
       </c>
       <c r="C3" t="n">
-        <v>6122</v>
+        <v>3841</v>
       </c>
       <c r="D3" t="n">
-        <v>14124</v>
+        <v>13083</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2227</v>
+        <v>2337</v>
       </c>
       <c r="C4" t="n">
-        <v>6777</v>
+        <v>4350</v>
       </c>
       <c r="D4" t="n">
-        <v>5257</v>
+        <v>6185</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1302</v>
+        <v>1367</v>
       </c>
       <c r="C5" t="n">
-        <v>3458</v>
+        <v>3813</v>
       </c>
       <c r="D5" t="n">
-        <v>1919</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>681</v>
+        <v>705</v>
       </c>
       <c r="C6" t="n">
-        <v>2303</v>
+        <v>2949</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>990</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C7" t="n">
-        <v>1404</v>
+        <v>1605</v>
       </c>
       <c r="D7" t="n">
-        <v>594</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>630</v>
+        <v>646</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_70_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_70_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4539</v>
+        <v>682</v>
       </c>
       <c r="C2" t="n">
-        <v>7662</v>
+        <v>2453</v>
       </c>
       <c r="D2" t="n">
-        <v>21288</v>
+        <v>17254</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3087</v>
+        <v>1316</v>
       </c>
       <c r="C3" t="n">
-        <v>3711</v>
+        <v>6220</v>
       </c>
       <c r="D3" t="n">
-        <v>13808</v>
+        <v>11777</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2486</v>
+        <v>1052</v>
       </c>
       <c r="C4" t="n">
-        <v>3953</v>
+        <v>9560</v>
       </c>
       <c r="D4" t="n">
-        <v>7129</v>
+        <v>4755</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1608</v>
+        <v>509</v>
       </c>
       <c r="C5" t="n">
-        <v>4006</v>
+        <v>5720</v>
       </c>
       <c r="D5" t="n">
-        <v>2829</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>914</v>
+        <v>223</v>
       </c>
       <c r="C6" t="n">
-        <v>3340</v>
+        <v>1705</v>
       </c>
       <c r="D6" t="n">
-        <v>1165</v>
+        <v>731</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>423</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>2234</v>
+        <v>567</v>
       </c>
       <c r="D7" t="n">
-        <v>657</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>156</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>1096</v>
+        <v>335</v>
       </c>
       <c r="D8" t="n">
-        <v>426</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>437</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5847</v>
+        <v>735</v>
       </c>
       <c r="C2" t="n">
-        <v>16589</v>
+        <v>10172</v>
       </c>
       <c r="D2" t="n">
-        <v>18725</v>
+        <v>22008</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3050</v>
+        <v>856</v>
       </c>
       <c r="C3" t="n">
-        <v>4846</v>
+        <v>3705</v>
       </c>
       <c r="D3" t="n">
-        <v>13897</v>
+        <v>11918</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2375</v>
+        <v>1028</v>
       </c>
       <c r="C4" t="n">
-        <v>3716</v>
+        <v>7533</v>
       </c>
       <c r="D4" t="n">
-        <v>8002</v>
+        <v>5891</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1753</v>
+        <v>671</v>
       </c>
       <c r="C5" t="n">
-        <v>3897</v>
+        <v>7683</v>
       </c>
       <c r="D5" t="n">
-        <v>3376</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1103</v>
+        <v>322</v>
       </c>
       <c r="C6" t="n">
-        <v>3575</v>
+        <v>3707</v>
       </c>
       <c r="D6" t="n">
-        <v>1404</v>
+        <v>895</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>571</v>
+        <v>137</v>
       </c>
       <c r="C7" t="n">
-        <v>2731</v>
+        <v>1118</v>
       </c>
       <c r="D7" t="n">
-        <v>718</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>234</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1575</v>
+        <v>442</v>
       </c>
       <c r="D8" t="n">
-        <v>455</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>714</v>
+        <v>312</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>305</v>
+        <v>244</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6424</v>
+        <v>391</v>
       </c>
       <c r="C2" t="n">
-        <v>20654</v>
+        <v>4200</v>
       </c>
       <c r="D2" t="n">
-        <v>21526</v>
+        <v>14809</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3388</v>
+        <v>790</v>
       </c>
       <c r="C3" t="n">
-        <v>8616</v>
+        <v>6085</v>
       </c>
       <c r="D3" t="n">
-        <v>13603</v>
+        <v>12885</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2262</v>
+        <v>1107</v>
       </c>
       <c r="C4" t="n">
-        <v>4137</v>
+        <v>6665</v>
       </c>
       <c r="D4" t="n">
-        <v>8664</v>
+        <v>6745</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1785</v>
+        <v>678</v>
       </c>
       <c r="C5" t="n">
-        <v>3702</v>
+        <v>8515</v>
       </c>
       <c r="D5" t="n">
-        <v>3907</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1245</v>
+        <v>272</v>
       </c>
       <c r="C6" t="n">
-        <v>3640</v>
+        <v>4813</v>
       </c>
       <c r="D6" t="n">
-        <v>1669</v>
+        <v>916</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>710</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>3077</v>
+        <v>1077</v>
       </c>
       <c r="D7" t="n">
-        <v>797</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>321</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>2012</v>
+        <v>461</v>
       </c>
       <c r="D8" t="n">
-        <v>486</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>1035</v>
+        <v>239</v>
       </c>
       <c r="D9" t="n">
-        <v>329</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>457</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>226</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5868</v>
+        <v>853</v>
       </c>
       <c r="C2" t="n">
-        <v>14044</v>
+        <v>6524</v>
       </c>
       <c r="D2" t="n">
-        <v>17743</v>
+        <v>15501</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4092</v>
+        <v>520</v>
       </c>
       <c r="C3" t="n">
-        <v>12417</v>
+        <v>4510</v>
       </c>
       <c r="D3" t="n">
-        <v>15114</v>
+        <v>12394</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1649</v>
+        <v>862</v>
       </c>
       <c r="C4" t="n">
-        <v>5857</v>
+        <v>6284</v>
       </c>
       <c r="D4" t="n">
-        <v>8439</v>
+        <v>7600</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1150</v>
+        <v>778</v>
       </c>
       <c r="C5" t="n">
-        <v>3567</v>
+        <v>7496</v>
       </c>
       <c r="D5" t="n">
-        <v>2685</v>
+        <v>3137</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>656</v>
+        <v>398</v>
       </c>
       <c r="C6" t="n">
-        <v>3015</v>
+        <v>6599</v>
       </c>
       <c r="D6" t="n">
-        <v>781</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>296</v>
+        <v>127</v>
       </c>
       <c r="C7" t="n">
-        <v>1971</v>
+        <v>2745</v>
       </c>
       <c r="D7" t="n">
-        <v>476</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>1014</v>
+        <v>717</v>
       </c>
       <c r="D8" t="n">
-        <v>322</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>447</v>
+        <v>326</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
         <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3652</v>
+        <v>438</v>
       </c>
       <c r="C2" t="n">
-        <v>5837</v>
+        <v>2820</v>
       </c>
       <c r="D2" t="n">
-        <v>13110</v>
+        <v>10778</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4178</v>
+        <v>560</v>
       </c>
       <c r="C3" t="n">
-        <v>11928</v>
+        <v>4913</v>
       </c>
       <c r="D3" t="n">
-        <v>14600</v>
+        <v>12102</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2239</v>
+        <v>691</v>
       </c>
       <c r="C4" t="n">
-        <v>8926</v>
+        <v>5516</v>
       </c>
       <c r="D4" t="n">
-        <v>9369</v>
+        <v>8251</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1275</v>
+        <v>794</v>
       </c>
       <c r="C5" t="n">
-        <v>4609</v>
+        <v>7127</v>
       </c>
       <c r="D5" t="n">
-        <v>3373</v>
+        <v>3628</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>774</v>
+        <v>476</v>
       </c>
       <c r="C6" t="n">
-        <v>3360</v>
+        <v>7189</v>
       </c>
       <c r="D6" t="n">
-        <v>977</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>279</v>
+        <v>142</v>
       </c>
       <c r="C7" t="n">
-        <v>2430</v>
+        <v>4065</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>652</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1322</v>
+        <v>1207</v>
       </c>
       <c r="D8" t="n">
-        <v>337</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>497</v>
+        <v>416</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3646</v>
+        <v>697</v>
       </c>
       <c r="C2" t="n">
-        <v>7376</v>
+        <v>14969</v>
       </c>
       <c r="D2" t="n">
-        <v>15606</v>
+        <v>12040</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3356</v>
+        <v>429</v>
       </c>
       <c r="C3" t="n">
-        <v>8039</v>
+        <v>3486</v>
       </c>
       <c r="D3" t="n">
-        <v>13416</v>
+        <v>11108</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2623</v>
+        <v>555</v>
       </c>
       <c r="C4" t="n">
-        <v>10210</v>
+        <v>5111</v>
       </c>
       <c r="D4" t="n">
-        <v>9937</v>
+        <v>8628</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1497</v>
+        <v>700</v>
       </c>
       <c r="C5" t="n">
-        <v>6543</v>
+        <v>6304</v>
       </c>
       <c r="D5" t="n">
-        <v>4191</v>
+        <v>4227</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>910</v>
+        <v>555</v>
       </c>
       <c r="C6" t="n">
-        <v>3923</v>
+        <v>7094</v>
       </c>
       <c r="D6" t="n">
-        <v>1309</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>411</v>
+        <v>233</v>
       </c>
       <c r="C7" t="n">
-        <v>2853</v>
+        <v>5419</v>
       </c>
       <c r="D7" t="n">
-        <v>577</v>
+        <v>746</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>143</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>1779</v>
+        <v>2338</v>
       </c>
       <c r="D8" t="n">
-        <v>356</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>808</v>
+        <v>706</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>330</v>
+        <v>293</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2152</v>
+        <v>473</v>
       </c>
       <c r="C2" t="n">
-        <v>3482</v>
+        <v>7904</v>
       </c>
       <c r="D2" t="n">
-        <v>10884</v>
+        <v>8766</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3333</v>
+        <v>605</v>
       </c>
       <c r="C3" t="n">
-        <v>7571</v>
+        <v>6882</v>
       </c>
       <c r="D3" t="n">
-        <v>13343</v>
+        <v>11944</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2883</v>
+        <v>918</v>
       </c>
       <c r="C4" t="n">
-        <v>10269</v>
+        <v>7136</v>
       </c>
       <c r="D4" t="n">
-        <v>10452</v>
+        <v>8802</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1577</v>
+        <v>558</v>
       </c>
       <c r="C5" t="n">
-        <v>8354</v>
+        <v>9640</v>
       </c>
       <c r="D5" t="n">
-        <v>4410</v>
+        <v>3936</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>749</v>
+        <v>215</v>
       </c>
       <c r="C6" t="n">
-        <v>4850</v>
+        <v>6979</v>
       </c>
       <c r="D6" t="n">
-        <v>1283</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="C7" t="n">
-        <v>3076</v>
+        <v>2291</v>
       </c>
       <c r="D7" t="n">
-        <v>577</v>
+        <v>597</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>1332</v>
+        <v>691</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>323</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2331</v>
+        <v>210</v>
       </c>
       <c r="C2" t="n">
-        <v>5102</v>
+        <v>3632</v>
       </c>
       <c r="D2" t="n">
-        <v>14553</v>
+        <v>6391</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2438</v>
+        <v>467</v>
       </c>
       <c r="C3" t="n">
-        <v>5099</v>
+        <v>6503</v>
       </c>
       <c r="D3" t="n">
-        <v>12240</v>
+        <v>10630</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2704</v>
+        <v>642</v>
       </c>
       <c r="C4" t="n">
-        <v>8884</v>
+        <v>6647</v>
       </c>
       <c r="D4" t="n">
-        <v>10578</v>
+        <v>8697</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1865</v>
+        <v>508</v>
       </c>
       <c r="C5" t="n">
-        <v>9106</v>
+        <v>7448</v>
       </c>
       <c r="D5" t="n">
-        <v>5145</v>
+        <v>4179</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>956</v>
+        <v>204</v>
       </c>
       <c r="C6" t="n">
-        <v>6300</v>
+        <v>6721</v>
       </c>
       <c r="D6" t="n">
-        <v>1686</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>283</v>
+        <v>55</v>
       </c>
       <c r="C7" t="n">
-        <v>3800</v>
+        <v>3045</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>2003</v>
+        <v>827</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>645</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>128</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1636</v>
+        <v>507</v>
       </c>
       <c r="C2" t="n">
-        <v>3015</v>
+        <v>12885</v>
       </c>
       <c r="D2" t="n">
-        <v>11514</v>
+        <v>7297</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2106</v>
+        <v>291</v>
       </c>
       <c r="C3" t="n">
-        <v>4635</v>
+        <v>4369</v>
       </c>
       <c r="D3" t="n">
-        <v>11969</v>
+        <v>9237</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2420</v>
+        <v>493</v>
       </c>
       <c r="C4" t="n">
-        <v>7428</v>
+        <v>6429</v>
       </c>
       <c r="D4" t="n">
-        <v>10565</v>
+        <v>8785</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2023</v>
+        <v>512</v>
       </c>
       <c r="C5" t="n">
-        <v>9187</v>
+        <v>6941</v>
       </c>
       <c r="D5" t="n">
-        <v>5611</v>
+        <v>4832</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1111</v>
+        <v>312</v>
       </c>
       <c r="C6" t="n">
-        <v>7402</v>
+        <v>7011</v>
       </c>
       <c r="D6" t="n">
-        <v>2014</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>256</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>4647</v>
+        <v>4874</v>
       </c>
       <c r="D7" t="n">
-        <v>740</v>
+        <v>712</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>2474</v>
+        <v>1856</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>728</v>
+        <v>511</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2522</v>
+        <v>565</v>
       </c>
       <c r="C2" t="n">
-        <v>9292</v>
+        <v>18293</v>
       </c>
       <c r="D2" t="n">
-        <v>14742</v>
+        <v>8803</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1637</v>
+        <v>315</v>
       </c>
       <c r="C3" t="n">
-        <v>3597</v>
+        <v>7373</v>
       </c>
       <c r="D3" t="n">
-        <v>11148</v>
+        <v>8322</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2009</v>
+        <v>354</v>
       </c>
       <c r="C4" t="n">
-        <v>6049</v>
+        <v>5266</v>
       </c>
       <c r="D4" t="n">
-        <v>10446</v>
+        <v>8596</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1970</v>
+        <v>456</v>
       </c>
       <c r="C5" t="n">
-        <v>8286</v>
+        <v>6550</v>
       </c>
       <c r="D5" t="n">
-        <v>6106</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1318</v>
+        <v>367</v>
       </c>
       <c r="C6" t="n">
-        <v>8097</v>
+        <v>6839</v>
       </c>
       <c r="D6" t="n">
-        <v>2437</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>464</v>
+        <v>172</v>
       </c>
       <c r="C7" t="n">
-        <v>5644</v>
+        <v>5856</v>
       </c>
       <c r="D7" t="n">
-        <v>882</v>
+        <v>897</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>3218</v>
+        <v>3186</v>
       </c>
       <c r="D8" t="n">
-        <v>440</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>1299</v>
+        <v>1077</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>382</v>
+        <v>315</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4583</v>
+        <v>3129</v>
       </c>
       <c r="C2" t="n">
-        <v>9638</v>
+        <v>4513</v>
       </c>
       <c r="D2" t="n">
-        <v>9891</v>
+        <v>9764</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1823</v>
+        <v>312</v>
       </c>
       <c r="C2" t="n">
-        <v>5352</v>
+        <v>22606</v>
       </c>
       <c r="D2" t="n">
-        <v>10968</v>
+        <v>16136</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2246</v>
+        <v>339</v>
       </c>
       <c r="C3" t="n">
-        <v>5189</v>
+        <v>10553</v>
       </c>
       <c r="D3" t="n">
-        <v>12229</v>
+        <v>7837</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2845</v>
+        <v>294</v>
       </c>
       <c r="C4" t="n">
-        <v>8777</v>
+        <v>6036</v>
       </c>
       <c r="D4" t="n">
-        <v>10791</v>
+        <v>8292</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1254</v>
+        <v>381</v>
       </c>
       <c r="C5" t="n">
-        <v>11756</v>
+        <v>5859</v>
       </c>
       <c r="D5" t="n">
-        <v>5590</v>
+        <v>5587</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>428</v>
+        <v>375</v>
       </c>
       <c r="C6" t="n">
-        <v>7038</v>
+        <v>6591</v>
       </c>
       <c r="D6" t="n">
-        <v>1946</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>221</v>
       </c>
       <c r="C7" t="n">
-        <v>3153</v>
+        <v>6258</v>
       </c>
       <c r="D7" t="n">
-        <v>543</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="C8" t="n">
-        <v>1273</v>
+        <v>4200</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>374</v>
+        <v>1882</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>157</v>
+        <v>591</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>61</v>
+      </c>
+      <c r="D13" t="n">
         <v>38</v>
-      </c>
-      <c r="D13" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6127</v>
+        <v>2958</v>
       </c>
       <c r="C2" t="n">
-        <v>8603</v>
+        <v>11412</v>
       </c>
       <c r="D2" t="n">
-        <v>14009</v>
+        <v>16467</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1948</v>
+        <v>1036</v>
       </c>
       <c r="C3" t="n">
-        <v>4857</v>
+        <v>1782</v>
       </c>
       <c r="D3" t="n">
-        <v>2301</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4285</v>
+        <v>2551</v>
       </c>
       <c r="C2" t="n">
-        <v>5907</v>
+        <v>7061</v>
       </c>
       <c r="D2" t="n">
-        <v>22895</v>
+        <v>15050</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3313</v>
+        <v>1683</v>
       </c>
       <c r="C3" t="n">
-        <v>6016</v>
+        <v>6532</v>
       </c>
       <c r="D3" t="n">
-        <v>4098</v>
+        <v>4359</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>880</v>
+        <v>506</v>
       </c>
       <c r="C4" t="n">
-        <v>2890</v>
+        <v>1159</v>
       </c>
       <c r="D4" t="n">
-        <v>1645</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5120</v>
+        <v>2511</v>
       </c>
       <c r="C2" t="n">
-        <v>7738</v>
+        <v>10959</v>
       </c>
       <c r="D2" t="n">
-        <v>31313</v>
+        <v>12017</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3119</v>
+        <v>1749</v>
       </c>
       <c r="C3" t="n">
-        <v>5156</v>
+        <v>5878</v>
       </c>
       <c r="D3" t="n">
-        <v>6810</v>
+        <v>5834</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1780</v>
+        <v>956</v>
       </c>
       <c r="C4" t="n">
-        <v>4600</v>
+        <v>4384</v>
       </c>
       <c r="D4" t="n">
-        <v>2065</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>414</v>
+        <v>266</v>
       </c>
       <c r="C5" t="n">
-        <v>1676</v>
+        <v>759</v>
       </c>
       <c r="D5" t="n">
-        <v>1231</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5245</v>
+        <v>1688</v>
       </c>
       <c r="C2" t="n">
-        <v>4374</v>
+        <v>9461</v>
       </c>
       <c r="D2" t="n">
-        <v>27174</v>
+        <v>16341</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3319</v>
+        <v>1749</v>
       </c>
       <c r="C3" t="n">
-        <v>5694</v>
+        <v>7517</v>
       </c>
       <c r="D3" t="n">
-        <v>10055</v>
+        <v>6403</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2056</v>
+        <v>1168</v>
       </c>
       <c r="C4" t="n">
-        <v>4753</v>
+        <v>5153</v>
       </c>
       <c r="D4" t="n">
-        <v>2867</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>900</v>
+        <v>521</v>
       </c>
       <c r="C5" t="n">
-        <v>3156</v>
+        <v>2761</v>
       </c>
       <c r="D5" t="n">
-        <v>1325</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>243</v>
+        <v>171</v>
       </c>
       <c r="C6" t="n">
-        <v>982</v>
+        <v>524</v>
       </c>
       <c r="D6" t="n">
-        <v>951</v>
+        <v>842</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>293</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>249</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5053</v>
+        <v>1236</v>
       </c>
       <c r="C2" t="n">
-        <v>6576</v>
+        <v>7233</v>
       </c>
       <c r="D2" t="n">
-        <v>21100</v>
+        <v>22133</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3091</v>
+        <v>1437</v>
       </c>
       <c r="C3" t="n">
-        <v>4126</v>
+        <v>7417</v>
       </c>
       <c r="D3" t="n">
-        <v>11242</v>
+        <v>7462</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1667</v>
+        <v>1237</v>
       </c>
       <c r="C4" t="n">
-        <v>4269</v>
+        <v>6339</v>
       </c>
       <c r="D4" t="n">
-        <v>3571</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>762</v>
+        <v>727</v>
       </c>
       <c r="C5" t="n">
-        <v>2907</v>
+        <v>3966</v>
       </c>
       <c r="D5" t="n">
-        <v>1246</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>269</v>
+        <v>301</v>
       </c>
       <c r="C6" t="n">
-        <v>1378</v>
+        <v>1656</v>
       </c>
       <c r="D6" t="n">
-        <v>772</v>
+        <v>899</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="C7" t="n">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5392</v>
+        <v>1186</v>
       </c>
       <c r="C2" t="n">
-        <v>4056</v>
+        <v>6938</v>
       </c>
       <c r="D2" t="n">
-        <v>23838</v>
+        <v>29961</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3366</v>
+        <v>1118</v>
       </c>
       <c r="C3" t="n">
-        <v>4779</v>
+        <v>6471</v>
       </c>
       <c r="D3" t="n">
-        <v>12070</v>
+        <v>9061</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2065</v>
+        <v>1151</v>
       </c>
       <c r="C4" t="n">
-        <v>4093</v>
+        <v>6694</v>
       </c>
       <c r="D4" t="n">
-        <v>4974</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1083</v>
+        <v>842</v>
       </c>
       <c r="C5" t="n">
-        <v>3644</v>
+        <v>5068</v>
       </c>
       <c r="D5" t="n">
-        <v>1676</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>474</v>
+        <v>449</v>
       </c>
       <c r="C6" t="n">
-        <v>2227</v>
+        <v>2747</v>
       </c>
       <c r="D6" t="n">
-        <v>852</v>
+        <v>979</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="C7" t="n">
-        <v>955</v>
+        <v>989</v>
       </c>
       <c r="D7" t="n">
-        <v>551</v>
+        <v>645</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>242</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3921</v>
+        <v>1129</v>
       </c>
       <c r="C2" t="n">
-        <v>4665</v>
+        <v>4273</v>
       </c>
       <c r="D2" t="n">
-        <v>24369</v>
+        <v>23423</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3576</v>
+        <v>1752</v>
       </c>
       <c r="C3" t="n">
-        <v>3841</v>
+        <v>9673</v>
       </c>
       <c r="D3" t="n">
-        <v>13083</v>
+        <v>10313</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2337</v>
+        <v>778</v>
       </c>
       <c r="C4" t="n">
-        <v>4350</v>
+        <v>9106</v>
       </c>
       <c r="D4" t="n">
-        <v>6185</v>
+        <v>3765</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1367</v>
+        <v>414</v>
       </c>
       <c r="C5" t="n">
-        <v>3813</v>
+        <v>2692</v>
       </c>
       <c r="D5" t="n">
-        <v>2210</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>705</v>
+        <v>168</v>
       </c>
       <c r="C6" t="n">
-        <v>2949</v>
+        <v>969</v>
       </c>
       <c r="D6" t="n">
-        <v>990</v>
+        <v>632</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>277</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>1605</v>
+        <v>341</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>646</v>
+        <v>281</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>237</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
